--- a/hema/4-扣款记录.xlsx
+++ b/hema/4-扣款记录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16360" activeTab="2"/>
+    <workbookView windowHeight="15520" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="3" r:id="rId1"/>
@@ -1540,7 +1540,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="11" vm="1" t="e" cm="1">
-        <f t="array" ref="A2">_xlfn.LET(_xlpm.类目匹配,ISNUMBER(MATCH(数据源!J:J,数据汇总!$B$2:$B$6,0)),_xlpm.状态筛选,数据源!O:O="计费成功",_xlfn._xlws.SORT(_xlfn._xlws.FILTER(数据源!A:S,_xlpm.类目匹配*_xlpm.状态筛选),10,1))</f>
+        <f t="array" ref="A2">_xlfn.LET(_xlpm.类目匹配,ISNUMBER(MATCH(数据源!J:J,数据汇总!$B$2:$B$6,0)),_xlpm.状态筛选,数据源!O:O="计费成功",_xlpm.筛选结果,_xlfn._xlws.FILTER(数据源!A:S,_xlpm.类目匹配*_xlpm.状态筛选),_xlpm.排序结果,_xlfn._xlws.SORT(_xlpm.筛选结果,10,1),IF(_xlpm.排序结果="","",_xlpm.排序结果))</f>
         <v>#VALUE!</v>
       </c>
     </row>
